--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136277264</v>
       </c>
       <c r="B5" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136277249</v>
       </c>
       <c r="B6" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136271964</v>
       </c>
       <c r="B7" t="n">
-        <v>93044</v>
+        <v>93047</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136276717</v>
       </c>
       <c r="B26" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>136277068</v>
       </c>
       <c r="B73" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>136277183</v>
       </c>
       <c r="B75" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136277198</v>
       </c>
       <c r="B76" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>136276878</v>
       </c>
       <c r="B77" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136276940</v>
       </c>
       <c r="B78" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136277264</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136277249</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136271964</v>
       </c>
       <c r="B7" t="n">
-        <v>93047</v>
+        <v>93048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136276717</v>
       </c>
       <c r="B26" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>136277068</v>
       </c>
       <c r="B73" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>136277183</v>
       </c>
       <c r="B75" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136277198</v>
       </c>
       <c r="B76" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>136276878</v>
       </c>
       <c r="B77" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136276940</v>
       </c>
       <c r="B78" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136277264</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136277249</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136271964</v>
       </c>
       <c r="B7" t="n">
-        <v>93048</v>
+        <v>93053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>136272648</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136272215</v>
       </c>
       <c r="B9" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>136272621</v>
       </c>
       <c r="B10" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>136276411</v>
       </c>
       <c r="B12" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136276717</v>
       </c>
       <c r="B26" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>136275098</v>
       </c>
       <c r="B37" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>136275148</v>
       </c>
       <c r="B38" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>136275244</v>
       </c>
       <c r="B39" t="n">
-        <v>78478</v>
+        <v>78480</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>136275528</v>
       </c>
       <c r="B40" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>136277068</v>
       </c>
       <c r="B73" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>136277183</v>
       </c>
       <c r="B75" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136277198</v>
       </c>
       <c r="B76" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>136276878</v>
       </c>
       <c r="B77" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136276940</v>
       </c>
       <c r="B78" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 18916-2022 artfynd.xlsx
+++ b/artfynd/A 18916-2022 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136277264</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136277249</v>
       </c>
       <c r="B6" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136271964</v>
       </c>
       <c r="B7" t="n">
-        <v>93053</v>
+        <v>93055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>136276717</v>
       </c>
       <c r="B26" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>136277068</v>
       </c>
       <c r="B73" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>136277183</v>
       </c>
       <c r="B75" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>136277198</v>
       </c>
       <c r="B76" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>136276878</v>
       </c>
       <c r="B77" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136276940</v>
       </c>
       <c r="B78" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
